--- a/results/hypothesis_1/mmlu/final_accuracies_mgsm.xlsx
+++ b/results/hypothesis_1/mmlu/final_accuracies_mgsm.xlsx
@@ -10,6 +10,7 @@
     <sheet name="cot_accuracy" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="direct_accuracy" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="cot_vs_direct_diff" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="flip_metrics" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1385,7 +1386,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1404,6 +1405,11 @@
           <t>accuracy_diff</t>
         </is>
       </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>relative_improvement</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1419,6 +1425,9 @@
       <c r="C2" t="n">
         <v>0.1588345864661654</v>
       </c>
+      <c r="D2" t="n">
+        <v>0.2363636363636364</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1434,6 +1443,9 @@
       <c r="C3" t="n">
         <v>0.1456766917293233</v>
       </c>
+      <c r="D3" t="n">
+        <v>0.223342939481268</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1449,6 +1461,9 @@
       <c r="C4" t="n">
         <v>0.1663533834586466</v>
       </c>
+      <c r="D4" t="n">
+        <v>0.2546762589928058</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1464,6 +1479,9 @@
       <c r="C5" t="n">
         <v>0.1644736842105263</v>
       </c>
+      <c r="D5" t="n">
+        <v>0.2713178294573644</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1479,6 +1497,9 @@
       <c r="C6" t="n">
         <v>0.1729323308270677</v>
       </c>
+      <c r="D6" t="n">
+        <v>0.2686131386861315</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1494,6 +1515,9 @@
       <c r="C7" t="n">
         <v>0.1447368421052631</v>
       </c>
+      <c r="D7" t="n">
+        <v>0.2268041237113401</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1509,6 +1533,9 @@
       <c r="C8" t="n">
         <v>0.1738721804511278</v>
       </c>
+      <c r="D8" t="n">
+        <v>0.2639087018544936</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1524,6 +1551,9 @@
       <c r="C9" t="n">
         <v>0.1766917293233083</v>
       </c>
+      <c r="D9" t="n">
+        <v>0.2629370629370629</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1537,6 +1567,303 @@
         </is>
       </c>
       <c r="C10" t="n">
+        <v>0.193609022556391</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.2938659058487875</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>language</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>n_paired</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>answer_change_rate</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>flip_to_correct_rate</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>flip_to_wrong_rate</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>net_flip_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>tiny-aya-earth</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>sw</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>1064</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.3994360902255639</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.2791353383458647</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.1203007518796992</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.1588345864661654</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>tiny-aya-fire</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>bn</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>1064</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.3975563909774436</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.2716165413533835</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.1259398496240602</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.1456766917293233</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>tiny-aya-fire</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>te</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1064</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.4107142857142857</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.2885338345864661</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.1221804511278195</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.1663533834586466</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>tiny-aya-global</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>1064</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.4295112781954887</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.2969924812030075</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.1325187969924812</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.1644736842105263</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>tiny-aya-global</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>zh</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1064</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.4266917293233083</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.299812030075188</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.1268796992481203</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.1729323308270677</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>tiny-aya-global</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>bn</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>1064</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.4135338345864661</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.2791353383458647</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.1343984962406015</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.1447368421052632</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>tiny-aya-global</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>te</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>1064</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.4426691729323308</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.3082706766917293</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.1343984962406015</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.1738721804511278</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>tiny-aya-global</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>sw</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>1064</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.3909774436090225</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.2838345864661654</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.1071428571428571</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.1766917293233083</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>tiny-aya-water</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>zh</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>1064</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.4172932330827068</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.3054511278195489</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.1118421052631579</v>
+      </c>
+      <c r="G10" t="n">
         <v>0.193609022556391</v>
       </c>
     </row>
